--- a/astro-site/public/dl/catering-checklist-templates/08-catering-commissary-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/08-catering-commissary-opening-closing-checklist.xlsx
@@ -715,7 +715,7 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>▸ Everything filled in daily is GREEN: Assigned to, Due by, ✓ Done, Initials and Notes.</t>
+          <t>▸ Everything filled in daily is GREEN: Assigned to, Due by (When, at closing), ✓ Done, Initials and Notes.</t>
         </is>
       </c>
     </row>
@@ -742,10 +742,10 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
+    <row r="21" ht="47" customHeight="1">
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>▸ "N/A" = not applicable at your commissary: that task comes OUT of the total (don't delete it, mark it N/A). "—" = not done: it still counts as pending and lowers the percentage, which is the point.</t>
+          <t>▸ "N/A" = doesn't apply (to this event, or to your commissary): that task comes OUT of the total (don't delete it, mark it N/A). "—" = not done: it still counts as pending and lowers the percentage, which is the point.</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Raise security gate and open front door</t>
+          <t>Raise the security gate and unlock the doors</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Load the insulated carriers for the events leaving first and log the departure temperature (hot 135 °F or above, cold 41 °F or below) — log reading: ____ °F (loading details go in the "Transport &amp; Delivery" sheet of 02-catering-transport-delivery-checklist.xlsx)</t>
+          <t>Check the transport vehicles: clean, fueled and the refrigeration on, pre-chilled to 41 °F or below before anything is loaded</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Outside</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -1124,13 +1124,13 @@
       <c r="G9" s="19" t="inlineStr"/>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="33.25" customHeight="1">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Turn on the POS / card terminal</t>
+          <t>Turn on the card terminal and the invoicing software (deposits and balances paid by card)</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Confirm the guaranteed count and any last-minute changes with each client</t>
+          <t>Call each client's day-of contact: confirm arrival time, site contact and any last-minute changes (the guaranteed count is already locked; extra guests are billed per the contract)</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Front desk</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Check the transport vehicles</t>
+          <t>Check the portable equipment</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Check the portable equipment</t>
+          <t>Review the day's order of events</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -1460,18 +1460,18 @@
       <c r="G21" s="19" t="inlineStr"/>
       <c r="H21" s="20" t="inlineStr"/>
     </row>
-    <row r="22" ht="24" customHeight="1">
+    <row r="22" ht="74" customHeight="1">
       <c r="A22" s="21" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>Review the day's order of events</t>
+          <t>Load the insulated carriers for the events leaving first and log the departure temperature (hot 135 °F or above, cold 41 °F or below) — log reading: ____ °F (loading details go in the Transport &amp; Delivery sheet of 02-catering-transport-delivery-checklist.xlsx)</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Outside</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>Turn off the commissary equipment that shouldn't run overnight (ovens, fryer, hood) and leave the walk-ins and blast chiller on</t>
+          <t>Unload and clean the delivery vehicles: returned food that still qualifies goes straight to the blast chiller or walk-in to finish cooling (FDA Food Code 3-501.14); the rest is discarded</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>Check that no staff or visitors are left in the commissary before closing</t>
+          <t>Check in the portable equipment that came back</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
@@ -1771,18 +1771,18 @@
       <c r="G7" s="19" t="inlineStr"/>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="33.25" customHeight="1">
       <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Turn off the POS / card terminal (or leave on standby)</t>
+          <t>Clear and hose down the loading dock: no carts, no pallets and no trash</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>Outside</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Close security gate and doors</t>
+          <t>Empty trash cans in common areas and restrooms</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Entrance</t>
+          <t>Restrooms</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -1827,13 +1827,13 @@
       <c r="G9" s="19" t="inlineStr"/>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="47" customHeight="1">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Turn off lights (leave security lighting)</t>
+          <t>Turn off the commissary equipment that shouldn't run overnight (ovens, fryer, hood) and leave the walk-ins and blast chiller on</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Turn off HVAC</t>
+          <t>Turn off the card terminal (or leave it on standby)</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>Clear and hose down the loading dock: no carts, no pallets and no trash</t>
+          <t>Final safety check (gas, water, outlets)</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Outside</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>Empty trash cans in common areas and restrooms</t>
+          <t>Turn off HVAC</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>Restrooms</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -1967,13 +1967,13 @@
       <c r="G14" s="19" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
+    <row r="15" ht="33.25" customHeight="1">
       <c r="A15" s="17" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Final safety check (gas, water, outlets)</t>
+          <t>Check that no staff or visitors are left in the commissary before closing</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Unload and clean the delivery vehicles</t>
+          <t>Turn off lights (leave security lighting)</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>Last one out</t>
+          <t>Ops manager</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -2029,17 +2029,17 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Check in the portable equipment that came back</t>
+          <t>Set the alarm</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Entrance</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Last one out</t>
+          <t>Ops manager</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Set the alarm</t>
+          <t>Close security gate and doors</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>Ops manager</t>
+          <t>Last one out</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
